--- a/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497612683536</v>
+        <v>10.84497617063473</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907122626863</v>
+        <v>37.78907137888654</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.069344234103029</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="C2" t="n">
-        <v>8.366453935591318</v>
+        <v>8.350745972323368</v>
       </c>
       <c r="D2" t="n">
-        <v>21.5768510439364</v>
+        <v>27.04518575659113</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.19959788359837</v>
+        <v>15.16309329209199</v>
       </c>
       <c r="C3" t="n">
-        <v>38.26852551154067</v>
+        <v>36.69282044622454</v>
       </c>
       <c r="D3" t="n">
-        <v>79.25158342532377</v>
+        <v>76.85121028844031</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.27393297168064</v>
+        <v>31.07722357793278</v>
       </c>
       <c r="C4" t="n">
-        <v>85.45917415927636</v>
+        <v>91.26621182989624</v>
       </c>
       <c r="D4" t="n">
-        <v>102.7781854098943</v>
+        <v>91.58527983377644</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.50276230222816</v>
+        <v>37.15915060574178</v>
       </c>
       <c r="C5" t="n">
-        <v>144.439630987312</v>
+        <v>132.8059206919873</v>
       </c>
       <c r="D5" t="n">
-        <v>75.0300682970625</v>
+        <v>66.46431957750907</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.0315234041897</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>163.38147119305</v>
+        <v>158.994040702771</v>
       </c>
       <c r="D6" t="n">
-        <v>49.14727182229959</v>
+        <v>44.51833139677587</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.23033516206628</v>
+        <v>23.05634483423634</v>
       </c>
       <c r="C7" t="n">
-        <v>147.8600399889079</v>
+        <v>164.2689711176891</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>93.96307277346222</v>
+        <v>115.7431455921777</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>59.01874498850123</v>
       </c>
       <c r="D9" t="n">
         <v>33.72499713628642</v>
@@ -895,7 +895,7 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
         <v>34.59188035913637</v>
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -965,7 +965,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.64002302496897</v>
+        <v>7.638273279915516</v>
       </c>
       <c r="C21" t="n">
-        <v>91.68027629962765</v>
+        <v>92.61406351897563</v>
       </c>
       <c r="D21" t="n">
-        <v>7.64002302496897</v>
+        <v>7.638273279915516</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.293002784222055</v>
+        <v>4.634830911749192</v>
       </c>
       <c r="C2" t="n">
-        <v>7.824529202847079</v>
+        <v>10.91114398499905</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8724392183727</v>
+        <v>25.43217427851362</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2045066221196</v>
+        <v>14.48077863764045</v>
       </c>
       <c r="C3" t="n">
-        <v>35.19565519724815</v>
+        <v>34.3660783871596</v>
       </c>
       <c r="D3" t="n">
-        <v>77.71514826817751</v>
+        <v>79.28103585645118</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.80622015383166</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="C4" t="n">
-        <v>89.18588844459724</v>
+        <v>91.22792366943061</v>
       </c>
       <c r="D4" t="n">
-        <v>115.5153801247924</v>
+        <v>105.4200684820225</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.80357801035519</v>
+        <v>41.30703465618456</v>
       </c>
       <c r="C5" t="n">
-        <v>150.207398749762</v>
+        <v>147.2130682518092</v>
       </c>
       <c r="D5" t="n">
-        <v>89.68265278294614</v>
+        <v>79.59519512181016</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.23027840880406</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>191.3161203696887</v>
+        <v>180.8104381865436</v>
       </c>
       <c r="D6" t="n">
-        <v>58.64666260859173</v>
+        <v>53.21268906558563</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.77604801690726</v>
+        <v>30.00319158948677</v>
       </c>
       <c r="C7" t="n">
-        <v>187.9241820515159</v>
+        <v>194.6314823669302</v>
       </c>
       <c r="D7" t="n">
-        <v>44.0765449298648</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.94420461177395</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C8" t="n">
-        <v>138.0239097400591</v>
+        <v>159.9708796684965</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>78.98749329288135</v>
+        <v>96.07186684218435</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1276,7 +1276,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1293,7 +1293,7 @@
         <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.807441884168233</v>
+        <v>7.804723795406614</v>
       </c>
       <c r="C21" t="n">
-        <v>99.54488402314496</v>
+        <v>100.4858188658602</v>
       </c>
       <c r="D21" t="n">
-        <v>8.783372119689261</v>
+        <v>8.780314269832441</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.102944640225672</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C2" t="n">
-        <v>10.18465068385641</v>
+        <v>12.86874890726719</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32360119396973</v>
+        <v>25.38406864100553</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.12029730373262</v>
+        <v>14.50532233024662</v>
       </c>
       <c r="C3" t="n">
-        <v>32.74128593663112</v>
+        <v>37.46349239405829</v>
       </c>
       <c r="D3" t="n">
-        <v>82.00538573573607</v>
+        <v>79.69336989223484</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.74691438094935</v>
+        <v>27.8099672181994</v>
       </c>
       <c r="C4" t="n">
-        <v>87.39910762286804</v>
+        <v>87.69265018643783</v>
       </c>
       <c r="D4" t="n">
-        <v>122.5221134900019</v>
+        <v>114.7368541953247</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.38633523605029</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="C5" t="n">
-        <v>154.0116711037184</v>
+        <v>153.8398652554752</v>
       </c>
       <c r="D5" t="n">
-        <v>103.8934508019187</v>
+        <v>92.94696389956678</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.53091419048183</v>
+        <v>45.88688769649593</v>
       </c>
       <c r="C6" t="n">
-        <v>208.9463456425529</v>
+        <v>202.546332358568</v>
       </c>
       <c r="D6" t="n">
-        <v>69.75611962984863</v>
+        <v>62.87308647537424</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.54323494228053</v>
+        <v>36.77037851486003</v>
       </c>
       <c r="C7" t="n">
-        <v>224.754447176335</v>
+        <v>220.3228380393649</v>
       </c>
       <c r="D7" t="n">
-        <v>48.68781389671206</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36974333606933</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="C8" t="n">
-        <v>181.5006068226291</v>
+        <v>198.6075605691297</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>12.20312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>115.0421777313455</v>
+        <v>136.1203009415245</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>63.48962403364123</v>
+        <v>73.88142348309373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>39.09319358310798</v>
+        <v>41.22554959673205</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.957949637268505</v>
+        <v>7.954823113734786</v>
       </c>
       <c r="C21" t="n">
-        <v>106.4375763984662</v>
+        <v>107.3901120354196</v>
       </c>
       <c r="D21" t="n">
-        <v>9.94743704658563</v>
+        <v>9.943528892168482</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.456954650831271</v>
+        <v>5.235660506748239</v>
       </c>
       <c r="C2" t="n">
-        <v>7.169703484114456</v>
+        <v>9.059567814789567</v>
       </c>
       <c r="D2" t="n">
-        <v>21.84584991490002</v>
+        <v>21.22440361811179</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.99543541884404</v>
+        <v>18.01016163440774</v>
       </c>
       <c r="C3" t="n">
-        <v>50.83980486442108</v>
+        <v>57.03463287821845</v>
       </c>
       <c r="D3" t="n">
-        <v>89.71701395259477</v>
+        <v>85.89310664455344</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.44213062427633</v>
+        <v>20.16509784522949</v>
       </c>
       <c r="C4" t="n">
-        <v>123.0198595760551</v>
+        <v>122.2540963667426</v>
       </c>
       <c r="D4" t="n">
-        <v>116.6640249387612</v>
+        <v>107.6663072293392</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.21266370338984</v>
+        <v>25.84450831429729</v>
       </c>
       <c r="C5" t="n">
-        <v>124.8537642875881</v>
+        <v>121.0249482410256</v>
       </c>
       <c r="D5" t="n">
-        <v>68.59962083424588</v>
+        <v>61.6537558266997</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.15728492132452</v>
+        <v>22.82268888062561</v>
       </c>
       <c r="C6" t="n">
-        <v>148.0053386491364</v>
+        <v>145.1072194261998</v>
       </c>
       <c r="D6" t="n">
-        <v>32.04031807579891</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="C7" t="n">
-        <v>127.6183658227471</v>
+        <v>139.6555744245173</v>
       </c>
       <c r="D7" t="n">
-        <v>28.02693346083794</v>
+        <v>27.5478405811655</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>84.78373173875454</v>
+        <v>100.3051629428966</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>56.35624521458389</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.37631247036279</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.909319358310799</v>
+        <v>3.268238107437631</v>
       </c>
       <c r="C2" t="n">
-        <v>3.48422260237193</v>
+        <v>4.28434698133308</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29170224134832</v>
+        <v>14.66534720603885</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.238728923048</v>
+        <v>18.38813450054276</v>
       </c>
       <c r="C3" t="n">
-        <v>40.40382676827748</v>
+        <v>47.32023934469626</v>
       </c>
       <c r="D3" t="n">
-        <v>87.18901361415924</v>
+        <v>83.66944809443441</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.84901614219102</v>
+        <v>25.98489823600458</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0483713172072</v>
+        <v>135.8974442126605</v>
       </c>
       <c r="D4" t="n">
-        <v>132.1452044870292</v>
+        <v>123.1091986171415</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.24979018970198</v>
+        <v>28.83883881225006</v>
       </c>
       <c r="C5" t="n">
-        <v>172.2230910174967</v>
+        <v>166.9461971071701</v>
       </c>
       <c r="D5" t="n">
-        <v>85.75566196595889</v>
+        <v>77.70533079113505</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.38370878810704</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>175.5777229229081</v>
+        <v>171.4318023678738</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52712606838509</v>
+        <v>36.4277485660779</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.16938468894497</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="C7" t="n">
-        <v>160.1966816404733</v>
+        <v>169.1796731343316</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>7.176575718044183</v>
       </c>
       <c r="C8" t="n">
-        <v>111.5707178491288</v>
+        <v>130.0128484734051</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.516620276612075</v>
+        <v>3.820962064928586</v>
       </c>
       <c r="C2" t="n">
-        <v>5.838453597155781</v>
+        <v>7.957065142920397</v>
       </c>
       <c r="D2" t="n">
-        <v>15.09142570968197</v>
+        <v>16.03684874887164</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92533042121501</v>
+        <v>14.91274762750905</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6102715236098</v>
+        <v>31.56318869153495</v>
       </c>
       <c r="D3" t="n">
-        <v>80.70457002760905</v>
+        <v>77.4402589109884</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.82196917482861</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>114.5581761131518</v>
+        <v>128.3163884404666</v>
       </c>
       <c r="D4" t="n">
-        <v>141.372651159245</v>
+        <v>132.6812387335479</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.2749557771139</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="C5" t="n">
-        <v>203.688104938607</v>
+        <v>205.1361828023711</v>
       </c>
       <c r="D5" t="n">
-        <v>108.9985388640021</v>
+        <v>99.77011044408214</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>31.79880814055419</v>
       </c>
       <c r="C6" t="n">
-        <v>219.089762922831</v>
+        <v>213.0520145417131</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>49.02651685467723</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="C7" t="n">
-        <v>203.2551542010341</v>
+        <v>206.0698248691097</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>155.2143120414207</v>
+        <v>171.5702287941726</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>85.97655519941439</v>
+        <v>99.28905406900114</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
         <v>16.84188186635403</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.38885420633975</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.116648050356123</v>
+        <v>2.285508655486574</v>
       </c>
       <c r="C2" t="n">
-        <v>2.810743677258618</v>
+        <v>3.937790041733956</v>
       </c>
       <c r="D2" t="n">
-        <v>10.55182432524472</v>
+        <v>11.32642326389545</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48354395430395</v>
+        <v>15.43307391075986</v>
       </c>
       <c r="C3" t="n">
-        <v>26.70844629403447</v>
+        <v>33.31560834361551</v>
       </c>
       <c r="D3" t="n">
-        <v>78.3483755374167</v>
+        <v>76.09035581764904</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.16580185549325</v>
+        <v>32.55769911593697</v>
       </c>
       <c r="C4" t="n">
-        <v>109.2233590882746</v>
+        <v>124.1940298303343</v>
       </c>
       <c r="D4" t="n">
-        <v>150.8553522345649</v>
+        <v>141.2833121181585</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.11573272257667</v>
+        <v>34.41025703385071</v>
       </c>
       <c r="C5" t="n">
-        <v>242.4425955637499</v>
+        <v>246.1977805324939</v>
       </c>
       <c r="D5" t="n">
-        <v>114.2018016965102</v>
+        <v>102.2735670899115</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.45162930614931</v>
+        <v>25.318291544821</v>
       </c>
       <c r="C6" t="n">
-        <v>252.6596439218464</v>
+        <v>249.2785048284204</v>
       </c>
       <c r="D6" t="n">
-        <v>51.80388110999145</v>
+        <v>47.73846386670541</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.425939634922873</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>208.9443821471444</v>
+        <v>216.9093012716988</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>121.9183386518901</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>8.679631453246051</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.279618169261094</v>
+        <v>2.486766934857171</v>
       </c>
       <c r="C2" t="n">
-        <v>7.283586217807087</v>
+        <v>7.801949005649402</v>
       </c>
       <c r="D2" t="n">
-        <v>11.09276731028471</v>
+        <v>12.32289718370596</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.14912784005428</v>
+        <v>11.84478605173777</v>
       </c>
       <c r="C3" t="n">
-        <v>18.98209186161208</v>
+        <v>24.50933143652162</v>
       </c>
       <c r="D3" t="n">
-        <v>69.92988897350031</v>
+        <v>68.60452957276711</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>30.9495963763807</v>
       </c>
       <c r="C4" t="n">
-        <v>88.99444764226911</v>
+        <v>105.8412382471444</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3778629974024</v>
+        <v>145.6736878515502</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.08614142272902</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>225.7283408989479</v>
+        <v>240.3072943070131</v>
       </c>
       <c r="D5" t="n">
-        <v>136.0456881160018</v>
+        <v>124.5346962837079</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.49566908412018</v>
+        <v>33.16736444027425</v>
       </c>
       <c r="C6" t="n">
-        <v>311.3465581863123</v>
+        <v>310.3805184453334</v>
       </c>
       <c r="D6" t="n">
-        <v>69.83662294159687</v>
+        <v>62.06805335789186</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.9117658798048</v>
+        <v>13.53437385074653</v>
       </c>
       <c r="C7" t="n">
-        <v>276.7360246207951</v>
+        <v>276.2569317411227</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>172.4881628976433</v>
+        <v>186.0902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>67.56093176315272</v>
+        <v>75.54843108490478</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -3103,7 +3103,7 @@
         <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
         <v>13.82791641431633</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>7.852999886270235</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.536435157146258</v>
+        <v>1.666025854106837</v>
       </c>
       <c r="C2" t="n">
-        <v>4.944081438586937</v>
+        <v>4.759512870188536</v>
       </c>
       <c r="D2" t="n">
-        <v>8.342891990689393</v>
+        <v>9.289296777583321</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.46052178874977</v>
+        <v>10.54397034361075</v>
       </c>
       <c r="C3" t="n">
-        <v>23.45886139297754</v>
+        <v>27.22386383876405</v>
       </c>
       <c r="D3" t="n">
-        <v>64.61372515500383</v>
+        <v>64.19648238069894</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.54569715930776</v>
+        <v>28.43534050580462</v>
       </c>
       <c r="C4" t="n">
-        <v>74.48323482579701</v>
+        <v>90.51321134073893</v>
       </c>
       <c r="D4" t="n">
-        <v>154.5820665198858</v>
+        <v>146.7202309042773</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.03767593232243</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="C5" t="n">
-        <v>209.1858920823892</v>
+        <v>232.1587883617645</v>
       </c>
       <c r="D5" t="n">
-        <v>151.4836707652829</v>
+        <v>139.5554361586841</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>341.5353000919017</v>
+        <v>346.9692736349078</v>
       </c>
       <c r="D6" t="n">
-        <v>82.11337798320324</v>
+        <v>73.45927197026759</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.29482741091031</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>337.6407069491545</v>
+        <v>332.3706852727576</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>219.8034935038184</v>
+        <v>235.4083732628214</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>79.5421807457808</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.498547907308132</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C2" t="n">
-        <v>13.20843361293659</v>
+        <v>5.053055433758333</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02640937702343</v>
+        <v>11.08491332865074</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.030696220738909</v>
+        <v>8.261406931236911</v>
       </c>
       <c r="C3" t="n">
-        <v>21.36773878293183</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D3" t="n">
-        <v>58.01638058246527</v>
+        <v>58.19800390775092</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.98940606389831</v>
+        <v>24.65757533986289</v>
       </c>
       <c r="C4" t="n">
-        <v>67.48926418074274</v>
+        <v>79.98396721269188</v>
       </c>
       <c r="D4" t="n">
-        <v>151.6849290446534</v>
+        <v>144.9717382430137</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.01313223971626</v>
+        <v>42.87783098297945</v>
       </c>
       <c r="C5" t="n">
-        <v>179.4880240289231</v>
+        <v>205.0134643393402</v>
       </c>
       <c r="D5" t="n">
-        <v>163.608254912731</v>
+        <v>151.7536513839507</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.53091419048183</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="C6" t="n">
-        <v>339.3214590188251</v>
+        <v>356.508916077074</v>
       </c>
       <c r="D6" t="n">
-        <v>101.7964377056475</v>
+        <v>91.89453036061421</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.01453059358123</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>397.6470901281281</v>
+        <v>400.3419875762855</v>
       </c>
       <c r="D7" t="n">
-        <v>52.22112388429633</v>
+        <v>49.28667999630262</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>305.3382622363217</v>
+        <v>308.9265500953438</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>140.55780056472</v>
+        <v>151.0968621698096</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.091744504851459</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.363287708300325</v>
+        <v>4.142975311921539</v>
       </c>
       <c r="C2" t="n">
-        <v>11.82515109765283</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="D2" t="n">
-        <v>12.73130422867264</v>
+        <v>6.805475085838889</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.824087234490574</v>
+        <v>1.457895340806514</v>
       </c>
       <c r="C2" t="n">
-        <v>7.819620464325845</v>
+        <v>2.991385254840031</v>
       </c>
       <c r="D2" t="n">
-        <v>8.947648576505429</v>
+        <v>8.247662463377454</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.93176068678823</v>
+        <v>10.98575681052181</v>
       </c>
       <c r="C3" t="n">
-        <v>32.85418692261951</v>
+        <v>26.22738991895354</v>
       </c>
       <c r="D3" t="n">
-        <v>63.5436201573748</v>
+        <v>63.25400458462199</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.395530818287</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="C4" t="n">
-        <v>99.76618345326513</v>
+        <v>116.5108722968987</v>
       </c>
       <c r="D4" t="n">
-        <v>154.3778629974024</v>
+        <v>146.9754853073815</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.62990647769474</v>
+        <v>25.81996462169112</v>
       </c>
       <c r="C5" t="n">
-        <v>278.2518430761523</v>
+        <v>304.73448739821</v>
       </c>
       <c r="D5" t="n">
-        <v>148.8084082712103</v>
+        <v>137.2483290537041</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>13.76606630894878</v>
       </c>
       <c r="C6" t="n">
-        <v>321.7717370577092</v>
+        <v>323.059790045681</v>
       </c>
       <c r="D6" t="n">
-        <v>79.13475544851842</v>
+        <v>72.69449050865934</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.551382356888213</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>214.6934967032137</v>
+        <v>217.208734321494</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.335176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>103.5596565824748</v>
+        <v>111.3203721845458</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>19.74687332322034</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>20.4988920646734</v>
       </c>
       <c r="D10" t="n">
         <v>18.79065105928395</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>4.916592502868027</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.343071917138642</v>
+        <v>6.003387211469246</v>
       </c>
       <c r="C2" t="n">
-        <v>7.382742735936014</v>
+        <v>9.348201639838129</v>
       </c>
       <c r="D2" t="n">
-        <v>20.2681813541754</v>
+        <v>14.57306292183965</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.39318210778423</v>
+        <v>8.806276907093888</v>
       </c>
       <c r="C3" t="n">
-        <v>29.7960428238907</v>
+        <v>39.11282853719293</v>
       </c>
       <c r="D3" t="n">
-        <v>13.82791641431632</v>
+        <v>8.850455553784995</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39686719901213</v>
+        <v>13.39745815706884</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13654004188703</v>
+        <v>70.13963388112511</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576102023413191</v>
+        <v>1.576171547890452</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.411393345808419</v>
+        <v>4.402156705842698</v>
       </c>
       <c r="C2" t="n">
-        <v>6.736752746541613</v>
+        <v>5.622469102221483</v>
       </c>
       <c r="D2" t="n">
-        <v>26.52780471645306</v>
+        <v>24.48282424850696</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69600236904876</v>
+        <v>15.91903902436203</v>
       </c>
       <c r="C3" t="n">
-        <v>29.16772429317274</v>
+        <v>37.44876617849459</v>
       </c>
       <c r="D3" t="n">
-        <v>27.50857067299563</v>
+        <v>18.95263943048468</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.29875440172729</v>
+        <v>10.37609148618454</v>
       </c>
       <c r="C4" t="n">
-        <v>45.94579255875072</v>
+        <v>60.13793737134262</v>
       </c>
       <c r="D4" t="n">
-        <v>22.32199755145973</v>
+        <v>19.70563991964198</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43604882781174</v>
+        <v>15.43713835869593</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1169039867392</v>
+        <v>86.12298242219833</v>
       </c>
       <c r="D21" t="n">
-        <v>3.24969449006563</v>
+        <v>3.249923864988617</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.347178834404876</v>
+        <v>4.177336481570178</v>
       </c>
       <c r="C2" t="n">
-        <v>12.64392868299467</v>
+        <v>6.631705742187204</v>
       </c>
       <c r="D2" t="n">
-        <v>25.41057582902019</v>
+        <v>25.469480691275</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.22614612934204</v>
+        <v>15.50179625005713</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38585220996478</v>
+        <v>28.14179794223482</v>
       </c>
       <c r="D3" t="n">
-        <v>42.34768722268617</v>
+        <v>34.14027641518283</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.81072798172539</v>
+        <v>21.60728522276805</v>
       </c>
       <c r="C4" t="n">
-        <v>61.63117562950202</v>
+        <v>79.61384832819084</v>
       </c>
       <c r="D4" t="n">
-        <v>31.07722357793278</v>
+        <v>24.77243982125977</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.78097245096173</v>
+        <v>9.547496423800233</v>
       </c>
       <c r="C5" t="n">
-        <v>49.87278337573798</v>
+        <v>64.52536786162162</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97414006898687</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
         <v>36.10573531908495</v>
@@ -5207,7 +5207,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72171034670163</v>
+        <v>16.72236898032709</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1663475975448</v>
+        <v>101.1703323309789</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180427586675407</v>
+        <v>4.180592245081773</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.107632394568655</v>
+        <v>4.370740779306799</v>
       </c>
       <c r="C2" t="n">
-        <v>6.182065293642165</v>
+        <v>8.939794594871456</v>
       </c>
       <c r="D2" t="n">
-        <v>24.09208866221672</v>
+        <v>30.81509694089889</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.38046044535803</v>
+        <v>14.81457285708437</v>
       </c>
       <c r="C3" t="n">
-        <v>39.64297229748621</v>
+        <v>26.74280746368311</v>
       </c>
       <c r="D3" t="n">
-        <v>52.23879534297278</v>
+        <v>45.90161391205962</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.40079940970673</v>
+        <v>26.09976271740145</v>
       </c>
       <c r="C4" t="n">
-        <v>65.39617807528853</v>
+        <v>74.54704842657306</v>
       </c>
       <c r="D4" t="n">
-        <v>44.54189334167778</v>
+        <v>35.68456555396306</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.07736244665303</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="C5" t="n">
-        <v>83.27674901273571</v>
+        <v>108.2376843932109</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9993056563988</v>
+        <v>32.15223731408305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="C6" t="n">
-        <v>46.85292743747478</v>
+        <v>57.80137783523521</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03444508569279</v>
+        <v>18.03437459977577</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7945015073438</v>
+        <v>116.7940450271193</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011481695230929</v>
+        <v>6.011458199925255</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.899902791895831</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C2" t="n">
-        <v>13.43227208950486</v>
+        <v>11.25181043837269</v>
       </c>
       <c r="D2" t="n">
-        <v>33.99595950265855</v>
+        <v>26.25487885467245</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.36649499332032</v>
+        <v>13.1897804065559</v>
       </c>
       <c r="C3" t="n">
-        <v>29.00573592197201</v>
+        <v>29.17263303169397</v>
       </c>
       <c r="D3" t="n">
-        <v>54.95332774521521</v>
+        <v>54.79624811253572</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.55172651425348</v>
+        <v>19.94813160259094</v>
       </c>
       <c r="C4" t="n">
-        <v>69.31433316293754</v>
+        <v>58.15971574728529</v>
       </c>
       <c r="D4" t="n">
-        <v>50.99982974021331</v>
+        <v>42.44880723622359</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.00940087088174</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C5" t="n">
-        <v>76.45360246822037</v>
+        <v>91.84249773228912</v>
       </c>
       <c r="D5" t="n">
-        <v>34.55751918948773</v>
+        <v>30.33600406122645</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>60.45798712292709</v>
+        <v>77.52468921355364</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>30.02773528209295</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>28.38625312059227</v>
+        <v>33.35684174719388</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>29.37389131106456</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.45305302221006</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,7 +5899,7 @@
         <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.042596551522211</v>
+        <v>7.041560926374179</v>
       </c>
       <c r="C21" t="n">
-        <v>66.02434267052072</v>
+        <v>66.01463368475792</v>
       </c>
       <c r="D21" t="n">
-        <v>4.401622844701381</v>
+        <v>4.400975578983862</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.860231973098458</v>
+        <v>4.425718650744621</v>
       </c>
       <c r="C2" t="n">
-        <v>5.952336330848412</v>
+        <v>10.70006822858599</v>
       </c>
       <c r="D2" t="n">
-        <v>28.12608997896687</v>
+        <v>26.62107074835651</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.57542732787565</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>43.63377671524949</v>
+        <v>38.37651775900782</v>
       </c>
       <c r="D3" t="n">
-        <v>70.22932202329558</v>
+        <v>63.60743375815085</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.88730430265664</v>
+        <v>23.39406604449724</v>
       </c>
       <c r="C4" t="n">
-        <v>70.76928326063133</v>
+        <v>66.74902641174064</v>
       </c>
       <c r="D4" t="n">
-        <v>67.96148482648545</v>
+        <v>61.3121076256218</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.17615911188346</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="C5" t="n">
-        <v>107.5995483854504</v>
+        <v>101.4390815413017</v>
       </c>
       <c r="D5" t="n">
-        <v>45.35674393620265</v>
+        <v>38.9508401659922</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.09186767803848</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>95.87944429215202</v>
+        <v>117.2933252171835</v>
       </c>
       <c r="D6" t="n">
-        <v>35.26045054572845</v>
+        <v>33.36862271964485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.06095047312131</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>62.10241452754048</v>
+        <v>78.3316858264445</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>33.21252483466959</v>
       </c>
       <c r="D8" t="n">
         <v>31.2097595180061</v>
@@ -6168,7 +6168,7 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
         <v>33.88011327355743</v>
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -6308,7 +6308,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256798068481713</v>
+        <v>7.255977382157586</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28927996049778</v>
+        <v>75.28076533988497</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442598551361285</v>
+        <v>5.44198303661819</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.64130223505142</v>
+        <v>4.0938879267092</v>
       </c>
       <c r="C2" t="n">
-        <v>11.40201783712246</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="D2" t="n">
-        <v>27.00002536219578</v>
+        <v>31.35996691675586</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28933783531232</v>
+        <v>16.72407214184441</v>
       </c>
       <c r="C3" t="n">
-        <v>31.58282364561989</v>
+        <v>40.60508504764808</v>
       </c>
       <c r="D3" t="n">
-        <v>75.98236357018189</v>
+        <v>69.68936078595983</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.6568145763369</v>
+        <v>30.13278228644735</v>
       </c>
       <c r="C4" t="n">
-        <v>92.64458560665875</v>
+        <v>82.47269764295756</v>
       </c>
       <c r="D4" t="n">
-        <v>86.14836104765762</v>
+        <v>77.83983022661685</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>30.55689729468198</v>
       </c>
       <c r="C5" t="n">
-        <v>120.3868122332651</v>
+        <v>113.5391219961436</v>
       </c>
       <c r="D5" t="n">
-        <v>59.54299826256906</v>
+        <v>52.15534678811181</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.86672865859647</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C6" t="n">
-        <v>135.8090869192783</v>
+        <v>140.9612988711656</v>
       </c>
       <c r="D6" t="n">
-        <v>41.49945720621693</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6874637104761</v>
+        <v>125.5822210841392</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>57.41260574435346</v>
+        <v>70.34713174780519</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>30.61874740004951</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
         <v>34.44952694202058</v>
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.456477740111919</v>
+        <v>7.455454554284631</v>
       </c>
       <c r="C21" t="n">
-        <v>83.8853745762591</v>
+        <v>83.8738637357021</v>
       </c>
       <c r="D21" t="n">
-        <v>6.52441802259793</v>
+        <v>6.523522734999053</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617063473</v>
+        <v>10.8449762987727</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907137888654</v>
+        <v>37.78907182538035</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.233296100712247</v>
+        <v>5.302419350637023</v>
       </c>
       <c r="C2" t="n">
-        <v>8.350745972323368</v>
+        <v>4.933282213840222</v>
       </c>
       <c r="D2" t="n">
-        <v>27.04518575659113</v>
+        <v>23.49813130114741</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.16309329209199</v>
+        <v>17.09222753093697</v>
       </c>
       <c r="C3" t="n">
-        <v>36.69282044622454</v>
+        <v>17.21985473248905</v>
       </c>
       <c r="D3" t="n">
-        <v>76.85121028844031</v>
+        <v>71.35342314465818</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.07722357793278</v>
+        <v>32.63427543686822</v>
       </c>
       <c r="C4" t="n">
-        <v>91.26621182989624</v>
+        <v>59.9592592891697</v>
       </c>
       <c r="D4" t="n">
-        <v>91.58527983377644</v>
+        <v>96.24367269042757</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.15915060574178</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>132.8059206919873</v>
+        <v>108.8021893231528</v>
       </c>
       <c r="D5" t="n">
-        <v>66.46431957750907</v>
+        <v>72.23208733995908</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>39.88939097125216</v>
       </c>
       <c r="C6" t="n">
-        <v>158.994040702771</v>
+        <v>110.5310470303314</v>
       </c>
       <c r="D6" t="n">
-        <v>44.51833139677587</v>
+        <v>49.26802678992194</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.05634483423634</v>
+        <v>28.50602634051038</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>86.29660495099888</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>115.7431455921777</v>
+        <v>57.24570863463151</v>
       </c>
       <c r="D8" t="n">
-        <v>34.96494448675015</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>59.01874498850123</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.638273279915516</v>
+        <v>7.702184890045975</v>
       </c>
       <c r="C21" t="n">
-        <v>92.61406351897563</v>
+        <v>95.31453801431894</v>
       </c>
       <c r="D21" t="n">
-        <v>7.638273279915516</v>
+        <v>8.664958001301722</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.634830911749192</v>
+        <v>5.858088551240718</v>
       </c>
       <c r="C2" t="n">
-        <v>10.91114398499905</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="D2" t="n">
-        <v>25.43217427851362</v>
+        <v>24.86472410545897</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48077863764045</v>
+        <v>17.41620427333842</v>
       </c>
       <c r="C3" t="n">
-        <v>34.3660783871596</v>
+        <v>18.16233252856599</v>
       </c>
       <c r="D3" t="n">
-        <v>79.28103585645118</v>
+        <v>72.83095343954963</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.50740899884213</v>
+        <v>32.68532631748906</v>
       </c>
       <c r="C4" t="n">
-        <v>91.22792366943061</v>
+        <v>50.6935244564883</v>
       </c>
       <c r="D4" t="n">
-        <v>105.4200684820225</v>
+        <v>106.9515949006475</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.30703465618456</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="C5" t="n">
-        <v>147.2130682518092</v>
+        <v>109.6366748717626</v>
       </c>
       <c r="D5" t="n">
-        <v>79.59519512181016</v>
+        <v>88.43092446003146</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>48.5434969841878</v>
       </c>
       <c r="C6" t="n">
-        <v>180.8104381865436</v>
+        <v>139.5927425714455</v>
       </c>
       <c r="D6" t="n">
-        <v>53.21268906558563</v>
+        <v>58.72716592033996</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.00319158948677</v>
+        <v>37.96811071404115</v>
       </c>
       <c r="C7" t="n">
-        <v>194.6314823669302</v>
+        <v>122.2285709264321</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>44.6155244194963</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>22.36421270274234</v>
       </c>
       <c r="C8" t="n">
-        <v>159.9708796684965</v>
+        <v>84.36648896444964</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>96.07186684218435</v>
+        <v>52.91718300660731</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.804723795406614</v>
+        <v>7.888020426480589</v>
       </c>
       <c r="C21" t="n">
-        <v>100.4858188658602</v>
+        <v>104.5162706508678</v>
       </c>
       <c r="D21" t="n">
-        <v>8.780314269832441</v>
+        <v>9.860025533100735</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.674501730546564</v>
+        <v>9.333475424274425</v>
       </c>
       <c r="C2" t="n">
-        <v>12.86874890726719</v>
+        <v>7.278677479285853</v>
       </c>
       <c r="D2" t="n">
-        <v>25.38406864100553</v>
+        <v>29.57220434732242</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.50532233024662</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="C3" t="n">
-        <v>37.46349239405829</v>
+        <v>21.57881453934489</v>
       </c>
       <c r="D3" t="n">
-        <v>79.69336989223484</v>
+        <v>74.642277953885</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.8099672181994</v>
+        <v>32.3024447128328</v>
       </c>
       <c r="C4" t="n">
-        <v>87.69265018643783</v>
+        <v>47.57942073861742</v>
       </c>
       <c r="D4" t="n">
-        <v>114.7368541953247</v>
+        <v>115.3239393224643</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="C5" t="n">
-        <v>153.8398652554752</v>
+        <v>101.9790427786374</v>
       </c>
       <c r="D5" t="n">
-        <v>92.94696389956678</v>
+        <v>103.7461886462817</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.88688769649593</v>
+        <v>54.78250364467628</v>
       </c>
       <c r="C6" t="n">
-        <v>202.546332358568</v>
+        <v>153.9223320626319</v>
       </c>
       <c r="D6" t="n">
-        <v>62.87308647537424</v>
+        <v>69.79637128572274</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>46.47200932822701</v>
       </c>
       <c r="C7" t="n">
-        <v>220.3228380393649</v>
+        <v>158.1605369018654</v>
       </c>
       <c r="D7" t="n">
-        <v>45.27427712904591</v>
+        <v>50.42452558552467</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.19869825135213</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="C8" t="n">
-        <v>198.6075605691297</v>
+        <v>117.9962565734241</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="C9" t="n">
-        <v>136.1203009415245</v>
+        <v>75.54843108490478</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>73.88142348309373</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.22554959673205</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.954823113734786</v>
+        <v>8.05946022556426</v>
       </c>
       <c r="C21" t="n">
-        <v>107.3901120354196</v>
+        <v>112.8324431578996</v>
       </c>
       <c r="D21" t="n">
-        <v>9.943528892168482</v>
+        <v>11.08175781015086</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.235660506748239</v>
+        <v>8.220173527658543</v>
       </c>
       <c r="C2" t="n">
-        <v>9.059567814789567</v>
+        <v>4.8321622003028</v>
       </c>
       <c r="D2" t="n">
-        <v>21.22440361811179</v>
+        <v>23.99391389179204</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.01016163440774</v>
+        <v>22.35930396422111</v>
       </c>
       <c r="C3" t="n">
-        <v>57.03463287821845</v>
+        <v>32.86400439966197</v>
       </c>
       <c r="D3" t="n">
-        <v>85.89310664455344</v>
+        <v>83.16875676526854</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.16509784522949</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="C4" t="n">
-        <v>122.2540963667426</v>
+        <v>77.85259294677206</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6663072293392</v>
+        <v>113.1542768960789</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.84450831429729</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="C5" t="n">
-        <v>121.0249482410256</v>
+        <v>91.96521619531997</v>
       </c>
       <c r="D5" t="n">
-        <v>61.6537558266997</v>
+        <v>70.58765993534568</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.82268888062561</v>
+        <v>28.86043726174349</v>
       </c>
       <c r="C6" t="n">
-        <v>145.1072194261998</v>
+        <v>104.1712854022206</v>
       </c>
       <c r="D6" t="n">
-        <v>29.78622534684823</v>
+        <v>33.20761609614837</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33097214951819</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>139.6555744245173</v>
+        <v>82.94295479329178</v>
       </c>
       <c r="D7" t="n">
-        <v>27.5478405811655</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>100.3051629428966</v>
+        <v>55.66018609227291</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>56.35624521458389</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
         <v>28.07602084605028</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>24.27567548291088</v>
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.268238107437631</v>
+        <v>4.73398742987812</v>
       </c>
       <c r="C2" t="n">
-        <v>4.28434698133308</v>
+        <v>2.352267499375358</v>
       </c>
       <c r="D2" t="n">
-        <v>14.66534720603885</v>
+        <v>16.1890196430299</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38813450054276</v>
+        <v>26.18812001078367</v>
       </c>
       <c r="C3" t="n">
-        <v>47.32023934469626</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D3" t="n">
-        <v>83.66944809443441</v>
+        <v>84.34194527184349</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.98489823600458</v>
+        <v>31.5494442236755</v>
       </c>
       <c r="C4" t="n">
-        <v>135.8974442126605</v>
+        <v>82.8555792476138</v>
       </c>
       <c r="D4" t="n">
-        <v>123.1091986171415</v>
+        <v>127.7165405931718</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.83883881225006</v>
+        <v>33.82120841130262</v>
       </c>
       <c r="C5" t="n">
-        <v>166.9461971071701</v>
+        <v>118.8405595990764</v>
       </c>
       <c r="D5" t="n">
-        <v>77.70533079113505</v>
+        <v>88.13640014875742</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>34.89818564286137</v>
       </c>
       <c r="C6" t="n">
-        <v>171.4318023678738</v>
+        <v>126.0279345418673</v>
       </c>
       <c r="D6" t="n">
-        <v>36.4277485660779</v>
+        <v>41.70071548558752</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.25301317025519</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>169.1796731343316</v>
+        <v>110.6704552043344</v>
       </c>
       <c r="D7" t="n">
-        <v>30.06307819944583</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0128484734051</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>43.37655881673681</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.820962064928586</v>
+        <v>4.896957548783091</v>
       </c>
       <c r="C2" t="n">
-        <v>7.957065142920397</v>
+        <v>4.28434698133308</v>
       </c>
       <c r="D2" t="n">
-        <v>16.03684874887164</v>
+        <v>14.74683226549134</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.91274762750905</v>
+        <v>21.04867077905162</v>
       </c>
       <c r="C3" t="n">
-        <v>31.56318869153495</v>
+        <v>16.81733817374786</v>
       </c>
       <c r="D3" t="n">
-        <v>77.4402589109884</v>
+        <v>78.04894248762143</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>41.07043345946106</v>
       </c>
       <c r="C4" t="n">
-        <v>128.3163884404666</v>
+        <v>73.38564089244908</v>
       </c>
       <c r="D4" t="n">
-        <v>132.6812387335479</v>
+        <v>139.6496839382918</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>40.34983064454391</v>
       </c>
       <c r="C5" t="n">
-        <v>205.1361828023711</v>
+        <v>137.3219601315226</v>
       </c>
       <c r="D5" t="n">
-        <v>99.77011044408214</v>
+        <v>111.133840120739</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.79880814055419</v>
+        <v>40.21140421824511</v>
       </c>
       <c r="C6" t="n">
-        <v>213.0520145417131</v>
+        <v>156.4984380385756</v>
       </c>
       <c r="D6" t="n">
-        <v>49.02651685467723</v>
+        <v>56.91584140600459</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>206.0698248691097</v>
+        <v>146.3029881299724</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>171.5702287941726</v>
+        <v>108.3162242095506</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>99.28905406900114</v>
+        <v>65.56405693271472</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.285508655486574</v>
+        <v>2.835287369864788</v>
       </c>
       <c r="C2" t="n">
-        <v>3.937790041733956</v>
+        <v>1.929134238844982</v>
       </c>
       <c r="D2" t="n">
-        <v>11.32642326389545</v>
+        <v>10.18465068385641</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.43307391075986</v>
+        <v>21.31374265919825</v>
       </c>
       <c r="C3" t="n">
-        <v>33.31560834361551</v>
+        <v>17.87271695581319</v>
       </c>
       <c r="D3" t="n">
-        <v>76.09035581764904</v>
+        <v>75.68783925890784</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>45.66501271533614</v>
       </c>
       <c r="C4" t="n">
-        <v>124.1940298303343</v>
+        <v>68.6506717148667</v>
       </c>
       <c r="D4" t="n">
-        <v>141.2833121181585</v>
+        <v>148.1751810019711</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.41025703385071</v>
+        <v>42.41150082346221</v>
       </c>
       <c r="C5" t="n">
-        <v>246.1977805324939</v>
+        <v>158.8467785471339</v>
       </c>
       <c r="D5" t="n">
-        <v>102.2735670899115</v>
+        <v>120.3868122332651</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.318291544821</v>
+        <v>34.89818564286137</v>
       </c>
       <c r="C6" t="n">
-        <v>249.2785048284204</v>
+        <v>192.2016567989193</v>
       </c>
       <c r="D6" t="n">
-        <v>47.73846386670541</v>
+        <v>55.78879504152925</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>216.9093012716988</v>
+        <v>149.9560713374748</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>121.9183386518901</v>
+        <v>83.28165775125692</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.486766934857171</v>
+        <v>3.806235849364884</v>
       </c>
       <c r="C2" t="n">
-        <v>7.801949005649402</v>
+        <v>4.388412237983243</v>
       </c>
       <c r="D2" t="n">
-        <v>12.32289718370596</v>
+        <v>13.52062938288707</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.84478605173777</v>
+        <v>15.59015354343935</v>
       </c>
       <c r="C3" t="n">
-        <v>24.50933143652162</v>
+        <v>12.41910845872215</v>
       </c>
       <c r="D3" t="n">
-        <v>68.60452957276711</v>
+        <v>67.637508084084</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.9495963763807</v>
+        <v>43.86546917345174</v>
       </c>
       <c r="C4" t="n">
-        <v>105.8412382471444</v>
+        <v>56.36017220540089</v>
       </c>
       <c r="D4" t="n">
-        <v>145.6736878515502</v>
+        <v>151.595590003567</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>53.92249265575607</v>
       </c>
       <c r="C5" t="n">
-        <v>240.3072943070131</v>
+        <v>144.439630987312</v>
       </c>
       <c r="D5" t="n">
-        <v>124.5346962837079</v>
+        <v>141.985261726695</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.16736444027425</v>
+        <v>44.07556318216056</v>
       </c>
       <c r="C6" t="n">
-        <v>310.3805184453334</v>
+        <v>224.2822265305924</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06805335789186</v>
+        <v>75.99512629033711</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.53437385074653</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>276.2569317411227</v>
+        <v>207.3274436782499</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>41.32176087174825</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>186.0902773399829</v>
+        <v>133.6845848872882</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>75.54843108490478</v>
+        <v>58.02030757328223</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.666025854106837</v>
+        <v>2.611448893296516</v>
       </c>
       <c r="C2" t="n">
-        <v>4.759512870188536</v>
+        <v>2.476949457814702</v>
       </c>
       <c r="D2" t="n">
-        <v>9.289296777583321</v>
+        <v>10.74326512757285</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.54397034361075</v>
+        <v>14.66240196292611</v>
       </c>
       <c r="C3" t="n">
-        <v>27.22386383876405</v>
+        <v>14.92256510455152</v>
       </c>
       <c r="D3" t="n">
-        <v>64.19648238069894</v>
+        <v>64.49100669197297</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.43534050580462</v>
+        <v>39.44956799974958</v>
       </c>
       <c r="C4" t="n">
-        <v>90.51321134073893</v>
+        <v>46.09894520061323</v>
       </c>
       <c r="D4" t="n">
-        <v>146.7202309042773</v>
+        <v>151.6976917648087</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>59.5920856477814</v>
       </c>
       <c r="C5" t="n">
-        <v>232.1587883617645</v>
+        <v>133.1249886958675</v>
       </c>
       <c r="D5" t="n">
-        <v>139.5554361586841</v>
+        <v>156.2451471308799</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>52.89067581859268</v>
       </c>
       <c r="C6" t="n">
-        <v>346.9692736349078</v>
+        <v>237.7665312484223</v>
       </c>
       <c r="D6" t="n">
-        <v>73.45927197026759</v>
+        <v>92.33729857522952</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.0970952117292</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>332.3706852727576</v>
+        <v>254.8774119857399</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>46.77144237802229</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>235.4083732628214</v>
+        <v>174.0736854400019</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.442187377538564</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>79.5421807457808</v>
+        <v>72.1093688769282</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.996874830438012</v>
+        <v>3.87495818866216</v>
       </c>
       <c r="C2" t="n">
-        <v>5.053055433758333</v>
+        <v>6.568873889115409</v>
       </c>
       <c r="D2" t="n">
-        <v>11.08491332865074</v>
+        <v>15.17880125535994</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.261406931236911</v>
+        <v>11.81533362061036</v>
       </c>
       <c r="C3" t="n">
-        <v>23.41468274628643</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="D3" t="n">
-        <v>58.19800390775092</v>
+        <v>58.88031856220246</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.65757533986289</v>
+        <v>34.17856457564846</v>
       </c>
       <c r="C4" t="n">
-        <v>79.98396721269188</v>
+        <v>41.83619666877358</v>
       </c>
       <c r="D4" t="n">
-        <v>144.9717382430137</v>
+        <v>149.5280293384232</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.87783098297945</v>
+        <v>59.49391087735672</v>
       </c>
       <c r="C5" t="n">
-        <v>205.0134643393402</v>
+        <v>112.4101121362598</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7536513839507</v>
+        <v>170.9959063871882</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>64.00013283984957</v>
       </c>
       <c r="C6" t="n">
-        <v>356.508916077074</v>
+        <v>227.8243722475149</v>
       </c>
       <c r="D6" t="n">
-        <v>91.89453036061421</v>
+        <v>113.1474046621492</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>35.2133266559246</v>
       </c>
       <c r="C7" t="n">
-        <v>400.3419875762855</v>
+        <v>293.5042754093307</v>
       </c>
       <c r="D7" t="n">
-        <v>49.28667999630262</v>
+        <v>57.79057861048849</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>308.9265500953438</v>
+        <v>243.0856403100315</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>151.0968621698096</v>
+        <v>127.3562391857132</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>51.67429041303087</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.142975311921539</v>
+        <v>5.237624002156734</v>
       </c>
       <c r="C2" t="n">
-        <v>15.52143120414207</v>
+        <v>4.150829293555514</v>
       </c>
       <c r="D2" t="n">
-        <v>6.805475085838889</v>
+        <v>7.357217295625596</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.457895340806514</v>
+        <v>2.712568906833937</v>
       </c>
       <c r="C2" t="n">
-        <v>2.991385254840031</v>
+        <v>3.62559427178347</v>
       </c>
       <c r="D2" t="n">
-        <v>8.247662463377454</v>
+        <v>11.17130712662446</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.98575681052181</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="C3" t="n">
-        <v>26.22738991895354</v>
+        <v>18.37340828497906</v>
       </c>
       <c r="D3" t="n">
-        <v>63.25400458462199</v>
+        <v>64.69226497134358</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.99163160121406</v>
+        <v>45.79263991688822</v>
       </c>
       <c r="C4" t="n">
-        <v>116.5108722968987</v>
+        <v>60.96751418143117</v>
       </c>
       <c r="D4" t="n">
-        <v>146.9754853073815</v>
+        <v>155.4116433299743</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.81996462169112</v>
+        <v>38.80357801035519</v>
       </c>
       <c r="C5" t="n">
-        <v>304.73448739821</v>
+        <v>181.7215000560846</v>
       </c>
       <c r="D5" t="n">
-        <v>137.2483290537041</v>
+        <v>157.8650308428871</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.76606630894878</v>
+        <v>21.85664913964674</v>
       </c>
       <c r="C6" t="n">
-        <v>323.059790045681</v>
+        <v>242.4357233298201</v>
       </c>
       <c r="D6" t="n">
-        <v>72.69449050865934</v>
+        <v>89.27817272879645</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.132176087174825</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>217.208734321494</v>
+        <v>170.9163848231442</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>111.3203721845458</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>39.38280915586078</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.003387211469246</v>
+        <v>6.57770961845363</v>
       </c>
       <c r="C2" t="n">
-        <v>9.348201639838129</v>
+        <v>6.007314202286233</v>
       </c>
       <c r="D2" t="n">
-        <v>14.57306292183965</v>
+        <v>22.53798204639403</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.806276907093888</v>
+        <v>11.1281102276376</v>
       </c>
       <c r="C3" t="n">
-        <v>39.11282853719293</v>
+        <v>10.62251015995049</v>
       </c>
       <c r="D3" t="n">
-        <v>8.850455553784995</v>
+        <v>9.611310024576275</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39745815706884</v>
+        <v>13.39912861565888</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13963388112511</v>
+        <v>70.14837922315533</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576171547890452</v>
+        <v>1.576368072430457</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.402156705842698</v>
+        <v>4.18911745402114</v>
       </c>
       <c r="C2" t="n">
-        <v>5.622469102221483</v>
+        <v>3.992767913171777</v>
       </c>
       <c r="D2" t="n">
-        <v>24.48282424850696</v>
+        <v>20.54307071136451</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.91903902436203</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C3" t="n">
-        <v>37.44876617849459</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D3" t="n">
-        <v>18.95263943048468</v>
+        <v>26.21757244191107</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.37609148618454</v>
+        <v>12.99244911800229</v>
       </c>
       <c r="C4" t="n">
-        <v>60.13793737134262</v>
+        <v>16.73192612347839</v>
       </c>
       <c r="D4" t="n">
-        <v>19.70563991964198</v>
+        <v>20.10128424445344</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43713835869593</v>
+        <v>15.44283569772917</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12298242219833</v>
+        <v>86.15476757680486</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249923864988617</v>
+        <v>3.251123304785089</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.177336481570178</v>
+        <v>4.679991306144545</v>
       </c>
       <c r="C2" t="n">
-        <v>6.631705742187204</v>
+        <v>6.137886646951058</v>
       </c>
       <c r="D2" t="n">
-        <v>25.469480691275</v>
+        <v>24.1775007124862</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50179625005713</v>
+        <v>16.05648370295658</v>
       </c>
       <c r="C3" t="n">
-        <v>28.14179794223482</v>
+        <v>16.75352457297182</v>
       </c>
       <c r="D3" t="n">
-        <v>34.14027641518283</v>
+        <v>36.56519324467245</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.60728522276805</v>
+        <v>25.35952494839936</v>
       </c>
       <c r="C4" t="n">
-        <v>79.61384832819084</v>
+        <v>34.34447993766616</v>
       </c>
       <c r="D4" t="n">
-        <v>24.77243982125977</v>
+        <v>28.71612034921921</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.547496423800233</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>64.52536786162162</v>
+        <v>19.88039101099791</v>
       </c>
       <c r="D5" t="n">
-        <v>30.0414797499524</v>
+        <v>29.67332436085985</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72236898032709</v>
+        <v>16.73913455240969</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1703323309789</v>
+        <v>102.1087207696991</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180592245081773</v>
+        <v>5.021740365722908</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.370740779306799</v>
+        <v>5.62050560681299</v>
       </c>
       <c r="C2" t="n">
-        <v>8.939794594871456</v>
+        <v>9.013425672689966</v>
       </c>
       <c r="D2" t="n">
-        <v>30.81509694089889</v>
+        <v>28.36465467109885</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.81457285708437</v>
+        <v>16.04666622591412</v>
       </c>
       <c r="C3" t="n">
-        <v>26.74280746368311</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D3" t="n">
-        <v>45.90161391205962</v>
+        <v>46.80482179996669</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.09976271740145</v>
+        <v>28.38428962518378</v>
       </c>
       <c r="C4" t="n">
-        <v>74.54704842657306</v>
+        <v>38.24987230515998</v>
       </c>
       <c r="D4" t="n">
-        <v>35.68456555396306</v>
+        <v>39.66653424238812</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.59215809657685</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="C5" t="n">
-        <v>108.2376843932109</v>
+        <v>43.83503499462009</v>
       </c>
       <c r="D5" t="n">
-        <v>32.15223731408305</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.418887474543901</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>57.80137783523521</v>
+        <v>22.42017232188442</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03437459977577</v>
+        <v>18.06962980824325</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7940450271193</v>
+        <v>117.8828230347298</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011458199925255</v>
+        <v>6.88366849837838</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.425538724295373</v>
+        <v>5.784457473422207</v>
       </c>
       <c r="C2" t="n">
-        <v>11.25181043837269</v>
+        <v>8.036586706964391</v>
       </c>
       <c r="D2" t="n">
-        <v>26.25487885467245</v>
+        <v>25.04634743074463</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.1897804065559</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C3" t="n">
-        <v>29.17263303169397</v>
+        <v>27.47911824186822</v>
       </c>
       <c r="D3" t="n">
-        <v>54.79624811253572</v>
+        <v>54.51645001682538</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.94813160259094</v>
+        <v>21.90082778633785</v>
       </c>
       <c r="C4" t="n">
-        <v>58.15971574728529</v>
+        <v>38.96458463385165</v>
       </c>
       <c r="D4" t="n">
-        <v>42.44880723622359</v>
+        <v>46.29038600294135</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.01507037292897</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="C5" t="n">
-        <v>91.84249773228912</v>
+        <v>43.51596699073988</v>
       </c>
       <c r="D5" t="n">
-        <v>30.33600406122645</v>
+        <v>32.61856747360028</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>77.52468921355364</v>
+        <v>31.71830482880595</v>
       </c>
       <c r="D6" t="n">
-        <v>30.02773528209295</v>
+        <v>30.91327171132357</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>33.35684174719388</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.041560926374179</v>
+        <v>7.064301441007871</v>
       </c>
       <c r="C21" t="n">
-        <v>66.01463368475792</v>
+        <v>66.22782600944879</v>
       </c>
       <c r="D21" t="n">
-        <v>4.400975578983862</v>
+        <v>5.298226080755904</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.425718650744621</v>
+        <v>4.464988558914493</v>
       </c>
       <c r="C2" t="n">
-        <v>10.70006822858599</v>
+        <v>4.217588137444298</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62107074835651</v>
+        <v>24.60063397301657</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="C3" t="n">
-        <v>38.37651775900782</v>
+        <v>30.06602344255857</v>
       </c>
       <c r="D3" t="n">
-        <v>63.60743375815085</v>
+        <v>62.86130550292327</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.39406604449724</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="C4" t="n">
-        <v>66.74902641174064</v>
+        <v>58.10866486666446</v>
       </c>
       <c r="D4" t="n">
-        <v>61.3121076256218</v>
+        <v>65.03882191094269</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.98547907308133</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="C5" t="n">
-        <v>101.4390815413017</v>
+        <v>61.28560043760715</v>
       </c>
       <c r="D5" t="n">
-        <v>38.9508401659922</v>
+        <v>42.97600575340413</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.07299348747954</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C6" t="n">
-        <v>117.2933252171835</v>
+        <v>54.13847715069036</v>
       </c>
       <c r="D6" t="n">
-        <v>33.36862271964485</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.863218273940204</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>78.3316858264445</v>
+        <v>34.2551408965797</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>33.21252483466959</v>
+        <v>21.44627859927157</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.255977382157586</v>
+        <v>7.289428980819857</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28076533988497</v>
+        <v>76.5390042986085</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44198303661819</v>
+        <v>6.378250358217374</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.0938879267092</v>
+        <v>5.069745144730529</v>
       </c>
       <c r="C2" t="n">
-        <v>8.623671834103982</v>
+        <v>3.57356164345839</v>
       </c>
       <c r="D2" t="n">
-        <v>31.35996691675586</v>
+        <v>24.35617879465912</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.72407214184441</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="C3" t="n">
-        <v>40.60508504764808</v>
+        <v>21.66717183272711</v>
       </c>
       <c r="D3" t="n">
-        <v>69.68936078595983</v>
+        <v>67.95657608796421</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.13278228644735</v>
+        <v>32.95334344074844</v>
       </c>
       <c r="C4" t="n">
-        <v>82.47269764295756</v>
+        <v>68.44646819238336</v>
       </c>
       <c r="D4" t="n">
-        <v>77.83983022661685</v>
+        <v>81.32405282898878</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.55689729468198</v>
+        <v>35.63744166415923</v>
       </c>
       <c r="C5" t="n">
-        <v>113.5391219961436</v>
+        <v>88.08731276354507</v>
       </c>
       <c r="D5" t="n">
-        <v>52.15534678811181</v>
+        <v>57.43224069843842</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.1635763181775</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>140.9612988711656</v>
+        <v>78.41022564278425</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>125.5822210841392</v>
+        <v>58.38944471007905</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>70.34713174780519</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.455454554284631</v>
+        <v>7.502500803504342</v>
       </c>
       <c r="C21" t="n">
-        <v>83.8738637357021</v>
+        <v>86.27875924029992</v>
       </c>
       <c r="D21" t="n">
-        <v>6.523522734999053</v>
+        <v>7.502500803504342</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_35_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449762987727</v>
+        <v>10.84497656259044</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907182538035</v>
+        <v>37.78907274464724</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.302419350637023</v>
+        <v>1.021017612416683</v>
       </c>
       <c r="C2" t="n">
-        <v>4.933282213840222</v>
+        <v>2.93935262651495</v>
       </c>
       <c r="D2" t="n">
-        <v>23.49813130114741</v>
+        <v>18.71603823376119</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.09222753093697</v>
+        <v>9.807659565425636</v>
       </c>
       <c r="C3" t="n">
-        <v>17.21985473248905</v>
+        <v>31.21466825652734</v>
       </c>
       <c r="D3" t="n">
-        <v>71.35342314465818</v>
+        <v>81.42615459023045</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.63427543686822</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C4" t="n">
-        <v>59.9592592891697</v>
+        <v>88.80300683994099</v>
       </c>
       <c r="D4" t="n">
-        <v>96.24367269042757</v>
+        <v>82.28125684062942</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>19.73312885536089</v>
       </c>
       <c r="C5" t="n">
-        <v>108.8021893231528</v>
+        <v>85.58385611771571</v>
       </c>
       <c r="D5" t="n">
-        <v>72.23208733995908</v>
+        <v>48.32653074154926</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.88939097125216</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>110.5310470303314</v>
+        <v>54.94351026817275</v>
       </c>
       <c r="D6" t="n">
-        <v>49.26802678992194</v>
+        <v>29.46421209985528</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.50602634051038</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>86.29660495099888</v>
+        <v>35.27321326588365</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.93729132011522</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>57.24570863463151</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
+        <v>32.06093477758807</v>
+      </c>
+      <c r="D9" t="n">
         <v>35.38905949498476</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.702184890045975</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.31453801431894</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.664958001301722</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.858088551240718</v>
+        <v>0.9493500300066655</v>
       </c>
       <c r="C2" t="n">
-        <v>6.563965150594174</v>
+        <v>5.165956419746716</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86472410545897</v>
+        <v>24.42097414313941</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.41620427333842</v>
+        <v>6.386268816125502</v>
       </c>
       <c r="C3" t="n">
-        <v>18.16233252856599</v>
+        <v>19.52205309894783</v>
       </c>
       <c r="D3" t="n">
-        <v>72.83095343954963</v>
+        <v>78.28947067516191</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.68532631748906</v>
+        <v>19.68011447933156</v>
       </c>
       <c r="C4" t="n">
-        <v>50.6935244564883</v>
+        <v>83.54476613599506</v>
       </c>
       <c r="D4" t="n">
-        <v>106.9515949006475</v>
+        <v>102.5867446075662</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.77398671050754</v>
+        <v>25.05911015089984</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6366748717626</v>
+        <v>128.7807551045754</v>
       </c>
       <c r="D5" t="n">
-        <v>88.43092446003146</v>
+        <v>67.34789251133121</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.5434969841878</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>139.5927425714455</v>
+        <v>98.33479530047329</v>
       </c>
       <c r="D6" t="n">
-        <v>58.72716592033996</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.96811071404115</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>122.2285709264321</v>
+        <v>58.32955810011999</v>
       </c>
       <c r="D7" t="n">
-        <v>44.6155244194963</v>
+        <v>31.50035683846316</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.36421270274234</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>84.36648896444964</v>
+        <v>38.55323234577224</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>52.91718300660731</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.24313893995049</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.888020426480589</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5162706508678</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.860025533100735</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.333475424274425</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>7.278677479285853</v>
+        <v>2.097013096271187</v>
       </c>
       <c r="D2" t="n">
-        <v>29.57220434732242</v>
+        <v>16.45409152317654</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.18687622117216</v>
+        <v>5.679410469067798</v>
       </c>
       <c r="C3" t="n">
-        <v>21.57881453934489</v>
+        <v>21.20084167320987</v>
       </c>
       <c r="D3" t="n">
-        <v>74.642277953885</v>
+        <v>81.76485754819561</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.3024447128328</v>
+        <v>21.27545449873262</v>
       </c>
       <c r="C4" t="n">
-        <v>47.57942073861742</v>
+        <v>77.40589774133977</v>
       </c>
       <c r="D4" t="n">
-        <v>115.3239393224643</v>
+        <v>116.0131262108456</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.97662764820988</v>
+        <v>25.57452769562942</v>
       </c>
       <c r="C5" t="n">
-        <v>101.9790427786374</v>
+        <v>153.520797251595</v>
       </c>
       <c r="D5" t="n">
-        <v>103.7461886462817</v>
+        <v>77.9998551024091</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.78250364467628</v>
+        <v>15.37613254391355</v>
       </c>
       <c r="C6" t="n">
-        <v>153.9223320626319</v>
+        <v>130.656874967391</v>
       </c>
       <c r="D6" t="n">
-        <v>69.79637128572274</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.47200932822701</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>158.1605369018654</v>
+        <v>59.34763046942393</v>
       </c>
       <c r="D7" t="n">
-        <v>50.42452558552467</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.45872252425729</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>117.9962565734241</v>
+        <v>39.63806355896497</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>75.54843108490478</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.05946022556426</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8324431578996</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08175781015086</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.220173527658543</v>
+        <v>1.244856088984956</v>
       </c>
       <c r="C2" t="n">
-        <v>4.8321622003028</v>
+        <v>4.735950925286613</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99391389179204</v>
+        <v>15.08749871886498</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.35930396422111</v>
+        <v>3.59810533606456</v>
       </c>
       <c r="C3" t="n">
-        <v>32.86400439966197</v>
+        <v>13.73465038241288</v>
       </c>
       <c r="D3" t="n">
-        <v>83.16875676526854</v>
+        <v>76.0854470791278</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.56448923440869</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C4" t="n">
-        <v>77.85259294677206</v>
+        <v>64.55383854504477</v>
       </c>
       <c r="D4" t="n">
-        <v>113.1542768960789</v>
+        <v>130.0904065420406</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>29.15790681613028</v>
       </c>
       <c r="C5" t="n">
-        <v>91.96521619531997</v>
+        <v>149.4220005863646</v>
       </c>
       <c r="D5" t="n">
-        <v>70.58765993534568</v>
+        <v>101.4390815413017</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.86043726174349</v>
+        <v>23.98998690097506</v>
       </c>
       <c r="C6" t="n">
-        <v>104.1712854022206</v>
+        <v>189.9878157258428</v>
       </c>
       <c r="D6" t="n">
-        <v>33.20761609614837</v>
+        <v>51.15985461600555</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>82.94295479329178</v>
+        <v>121.3302717770463</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>55.66018609227291</v>
+        <v>58.0801941832413</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73398742987812</v>
+        <v>0.6960591223109885</v>
       </c>
       <c r="C2" t="n">
-        <v>2.352267499375358</v>
+        <v>2.885356502781375</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1890196430299</v>
+        <v>12.02346413391069</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.18812001078367</v>
+        <v>4.000621894805753</v>
       </c>
       <c r="C3" t="n">
-        <v>26.01631416254048</v>
+        <v>16.57190124768616</v>
       </c>
       <c r="D3" t="n">
-        <v>84.34194527184349</v>
+        <v>71.61358628628358</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.5494442236755</v>
+        <v>12.89034735676062</v>
       </c>
       <c r="C4" t="n">
-        <v>82.8555792476138</v>
+        <v>51.49757582626644</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7165405931718</v>
+        <v>137.7863267956313</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.82120841130262</v>
+        <v>29.57514959043517</v>
       </c>
       <c r="C5" t="n">
-        <v>118.8405595990764</v>
+        <v>141.3716694115407</v>
       </c>
       <c r="D5" t="n">
-        <v>88.13640014875742</v>
+        <v>120.2886374628405</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.89818564286137</v>
+        <v>28.94094057349173</v>
       </c>
       <c r="C6" t="n">
-        <v>126.0279345418673</v>
+        <v>217.8419615907333</v>
       </c>
       <c r="D6" t="n">
-        <v>41.70071548558752</v>
+        <v>63.67811959285662</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>110.6704552043344</v>
+        <v>178.5818708979033</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>87.62098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>43.37655881673681</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.896957548783091</v>
+        <v>0.585121631731099</v>
       </c>
       <c r="C2" t="n">
-        <v>4.28434698133308</v>
+        <v>3.11508546557513</v>
       </c>
       <c r="D2" t="n">
-        <v>14.74683226549134</v>
+        <v>24.66052058297563</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.04867077905162</v>
+        <v>3.171045084717198</v>
       </c>
       <c r="C3" t="n">
-        <v>16.81733817374786</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="D3" t="n">
-        <v>78.04894248762143</v>
+        <v>65.71819132228148</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.07043345946106</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="C4" t="n">
-        <v>73.38564089244908</v>
+        <v>46.30314872309656</v>
       </c>
       <c r="D4" t="n">
-        <v>139.6496839382918</v>
+        <v>141.4875156406418</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.34983064454391</v>
+        <v>25.45180923259857</v>
       </c>
       <c r="C5" t="n">
-        <v>137.3219601315226</v>
+        <v>118.49694790259</v>
       </c>
       <c r="D5" t="n">
-        <v>111.133840120739</v>
+        <v>137.6901155206152</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>34.49566908412018</v>
       </c>
       <c r="C6" t="n">
-        <v>156.4984380385756</v>
+        <v>224.16147156297</v>
       </c>
       <c r="D6" t="n">
-        <v>56.91584140600459</v>
+        <v>83.32092765942681</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>146.3029881299724</v>
+        <v>241.2232649150752</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>48.38838084691679</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>108.3162242095506</v>
+        <v>154.7970692671158</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>42.55876297909923</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>65.56405693271472</v>
+        <v>74.43905617910588</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.835287369864788</v>
+        <v>0.3877903431774901</v>
       </c>
       <c r="C2" t="n">
-        <v>1.929134238844982</v>
+        <v>1.59435827169682</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18465068385641</v>
+        <v>17.75588897900781</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.31374265919825</v>
+        <v>4.187153958612646</v>
       </c>
       <c r="C3" t="n">
-        <v>17.87271695581319</v>
+        <v>15.33980787885641</v>
       </c>
       <c r="D3" t="n">
-        <v>75.68783925890784</v>
+        <v>74.93189352663781</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.66501271533614</v>
+        <v>17.28072309015236</v>
       </c>
       <c r="C4" t="n">
-        <v>68.6506717148667</v>
+        <v>66.02155136289375</v>
       </c>
       <c r="D4" t="n">
-        <v>148.1751810019711</v>
+        <v>145.7885523329471</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.41150082346221</v>
+        <v>21.30392518215579</v>
       </c>
       <c r="C5" t="n">
-        <v>158.8467785471339</v>
+        <v>183.2922963828795</v>
       </c>
       <c r="D5" t="n">
-        <v>120.3868122332651</v>
+        <v>126.9890655443249</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.89818564286137</v>
+        <v>12.71952325622168</v>
       </c>
       <c r="C6" t="n">
-        <v>192.2016567989193</v>
+        <v>215.9903854205238</v>
       </c>
       <c r="D6" t="n">
-        <v>55.78879504152925</v>
+        <v>69.51460969460392</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C7" t="n">
-        <v>149.9560713374748</v>
+        <v>108.8139702956037</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>54.82570054366312</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.806235849364884</v>
+        <v>0.2179479903427919</v>
       </c>
       <c r="C2" t="n">
-        <v>4.388412237983243</v>
+        <v>1.299833960422777</v>
       </c>
       <c r="D2" t="n">
-        <v>13.52062938288707</v>
+        <v>12.36609408269282</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59015354343935</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C3" t="n">
-        <v>12.41910845872215</v>
+        <v>10.24453729381547</v>
       </c>
       <c r="D3" t="n">
-        <v>67.637508084084</v>
+        <v>71.54977268550753</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.86546917345174</v>
+        <v>11.90761790480956</v>
       </c>
       <c r="C4" t="n">
-        <v>56.36017220540089</v>
+        <v>49.73632044484766</v>
       </c>
       <c r="D4" t="n">
-        <v>151.595590003567</v>
+        <v>143.5678390259408</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.92249265575607</v>
+        <v>19.09499284760047</v>
       </c>
       <c r="C5" t="n">
-        <v>144.439630987312</v>
+        <v>138.8436690731052</v>
       </c>
       <c r="D5" t="n">
-        <v>141.985261726695</v>
+        <v>133.2477071588984</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>224.2822265305924</v>
+        <v>207.8595509339517</v>
       </c>
       <c r="D6" t="n">
-        <v>75.99512629033711</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>207.3274436782499</v>
+        <v>146.1233283000953</v>
       </c>
       <c r="D7" t="n">
-        <v>41.32176087174825</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>133.6845848872882</v>
+        <v>60.66709938393165</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>58.02030757328223</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>13.86031408855647</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.611448893296516</v>
+        <v>0.3544109212330985</v>
       </c>
       <c r="C2" t="n">
-        <v>2.476949457814702</v>
+        <v>5.419247327442394</v>
       </c>
       <c r="D2" t="n">
-        <v>10.74326512757285</v>
+        <v>11.388273369263</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.66240196292611</v>
+        <v>1.644427404613407</v>
       </c>
       <c r="C3" t="n">
-        <v>14.92256510455152</v>
+        <v>7.098035901704439</v>
       </c>
       <c r="D3" t="n">
-        <v>64.49100669197297</v>
+        <v>64.8395271269806</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.44956799974958</v>
+        <v>8.397869862127216</v>
       </c>
       <c r="C4" t="n">
-        <v>46.09894520061323</v>
+        <v>35.60798923303181</v>
       </c>
       <c r="D4" t="n">
-        <v>151.6976917648087</v>
+        <v>147.3456041918825</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.5920856477814</v>
+        <v>19.02136176978195</v>
       </c>
       <c r="C5" t="n">
-        <v>133.1249886958675</v>
+        <v>113.6372967665683</v>
       </c>
       <c r="D5" t="n">
-        <v>156.2451471308799</v>
+        <v>155.2388557340269</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.89067581859268</v>
+        <v>19.40129813132547</v>
       </c>
       <c r="C6" t="n">
-        <v>237.7665312484223</v>
+        <v>215.7891271411532</v>
       </c>
       <c r="D6" t="n">
-        <v>92.33729857522952</v>
+        <v>99.50209332082274</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.8823545064064</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>254.8774119857399</v>
+        <v>230.6233349523225</v>
       </c>
       <c r="D7" t="n">
-        <v>46.77144237802229</v>
+        <v>49.0471335564664</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>174.0736854400019</v>
+        <v>129.8459513636831</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>72.1093688769282</v>
+        <v>53.24999547834697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>17.76963344686726</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.87495818866216</v>
+        <v>0.3347759671481623</v>
       </c>
       <c r="C2" t="n">
-        <v>6.568873889115409</v>
+        <v>6.992007149645783</v>
       </c>
       <c r="D2" t="n">
-        <v>15.17880125535994</v>
+        <v>15.01288589334223</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.81533362061036</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C3" t="n">
-        <v>12.24730261047896</v>
+        <v>14.98637870532756</v>
       </c>
       <c r="D3" t="n">
-        <v>58.88031856220246</v>
+        <v>59.69516915672731</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.17856457564846</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C4" t="n">
-        <v>41.83619666877358</v>
+        <v>25.80622015383166</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5280293384232</v>
+        <v>145.112128164721</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.49391087735672</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C5" t="n">
-        <v>112.4101121362598</v>
+        <v>88.28366230439444</v>
       </c>
       <c r="D5" t="n">
-        <v>170.9959063871882</v>
+        <v>172.6403337918016</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.00013283984957</v>
+        <v>22.82268888062561</v>
       </c>
       <c r="C6" t="n">
-        <v>227.8243722475149</v>
+        <v>199.0846899533937</v>
       </c>
       <c r="D6" t="n">
-        <v>113.1474046621492</v>
+        <v>123.4518285659237</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>293.5042754093307</v>
+        <v>273.9213539527195</v>
       </c>
       <c r="D7" t="n">
-        <v>57.79057861048849</v>
+        <v>63.53969316655781</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>243.0856403100315</v>
+        <v>217.9676252968769</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>127.3562391857132</v>
+        <v>105.8343660132146</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.67429041303087</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.237624002156734</v>
+        <v>4.321653394094459</v>
       </c>
       <c r="C2" t="n">
-        <v>4.150829293555514</v>
+        <v>7.105889883338413</v>
       </c>
       <c r="D2" t="n">
-        <v>7.357217295625596</v>
+        <v>4.732023934469626</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.712568906833937</v>
+        <v>0.5114905539125882</v>
       </c>
       <c r="C2" t="n">
-        <v>3.62559427178347</v>
+        <v>9.878345400131407</v>
       </c>
       <c r="D2" t="n">
-        <v>11.17130712662446</v>
+        <v>26.57983734477815</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>1.271363276999619</v>
       </c>
       <c r="C3" t="n">
-        <v>18.37340828497906</v>
+        <v>21.1762979806037</v>
       </c>
       <c r="D3" t="n">
-        <v>64.69226497134358</v>
+        <v>57.77094365640355</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.79263991688822</v>
+        <v>4.160646770597982</v>
       </c>
       <c r="C4" t="n">
-        <v>60.96751418143117</v>
+        <v>31.57496966398591</v>
       </c>
       <c r="D4" t="n">
-        <v>155.4116433299743</v>
+        <v>142.3426178910408</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.80357801035519</v>
+        <v>12.98361338866407</v>
       </c>
       <c r="C5" t="n">
-        <v>181.7215000560846</v>
+        <v>67.76513528563609</v>
       </c>
       <c r="D5" t="n">
-        <v>157.8650308428871</v>
+        <v>182.065111752571</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>22.62143060125501</v>
       </c>
       <c r="C6" t="n">
-        <v>242.4357233298201</v>
+        <v>172.5991003882233</v>
       </c>
       <c r="D6" t="n">
-        <v>89.27817272879645</v>
+        <v>146.3147691024234</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.94684675525043</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="C7" t="n">
-        <v>170.9163848231442</v>
+        <v>283.6229847660865</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>79.88873768537994</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>284.7264691856599</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>43.47669708257</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>181.4937345886993</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>80.28732725330416</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.90198946049134</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.57770961845363</v>
+        <v>5.828636120113313</v>
       </c>
       <c r="C2" t="n">
-        <v>6.007314202286233</v>
+        <v>4.908738521234052</v>
       </c>
       <c r="D2" t="n">
-        <v>22.53798204639403</v>
+        <v>20.6225922754085</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.1281102276376</v>
+        <v>7.142214548395545</v>
       </c>
       <c r="C3" t="n">
-        <v>10.62251015995049</v>
+        <v>14.02917469368692</v>
       </c>
       <c r="D3" t="n">
-        <v>9.611310024576275</v>
+        <v>6.297911522743289</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39912861565888</v>
+        <v>11.67883230522566</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14837922315533</v>
+        <v>59.95133916682506</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576368072430457</v>
+        <v>0.7785888203483773</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.18911745402114</v>
+        <v>3.404701038327938</v>
       </c>
       <c r="C2" t="n">
-        <v>3.992767913171777</v>
+        <v>4.399211462729958</v>
       </c>
       <c r="D2" t="n">
-        <v>20.54307071136451</v>
+        <v>18.55895860108171</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06415775814131</v>
+        <v>15.38889526406875</v>
       </c>
       <c r="C3" t="n">
-        <v>18.63357142660446</v>
+        <v>17.47510913559323</v>
       </c>
       <c r="D3" t="n">
-        <v>26.21757244191107</v>
+        <v>22.85999529338698</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.99244911800229</v>
+        <v>8.908378668335558</v>
       </c>
       <c r="C4" t="n">
-        <v>16.73192612347839</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="D4" t="n">
-        <v>20.10128424445344</v>
+        <v>17.44663845217007</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>21.07812321017901</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44283569772917</v>
+        <v>13.63105894963089</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15476757680486</v>
+        <v>73.76808372741422</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251123304785089</v>
+        <v>1.603653994074222</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.679991306144545</v>
+        <v>2.761656292046278</v>
       </c>
       <c r="C2" t="n">
-        <v>6.137886646951058</v>
+        <v>5.191481860057134</v>
       </c>
       <c r="D2" t="n">
-        <v>24.1775007124862</v>
+        <v>27.20717412779186</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05648370295658</v>
+        <v>13.37140373184156</v>
       </c>
       <c r="C3" t="n">
-        <v>16.75352457297182</v>
+        <v>17.28857707178633</v>
       </c>
       <c r="D3" t="n">
-        <v>36.56519324467245</v>
+        <v>32.92290926191679</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.35952494839936</v>
+        <v>21.44136986075034</v>
       </c>
       <c r="C4" t="n">
-        <v>34.34447993766616</v>
+        <v>36.22059980048183</v>
       </c>
       <c r="D4" t="n">
-        <v>28.71612034921921</v>
+        <v>25.20637230653686</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.73188506574938</v>
+        <v>8.565748719553422</v>
       </c>
       <c r="C5" t="n">
-        <v>19.88039101099791</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="D5" t="n">
-        <v>29.67332436085985</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73913455240969</v>
+        <v>14.84482871236968</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1087207696991</v>
+        <v>87.41954686173257</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021740365722908</v>
+        <v>2.47413811872828</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.62050560681299</v>
+        <v>2.083268628411731</v>
       </c>
       <c r="C2" t="n">
-        <v>9.013425672689966</v>
+        <v>5.197372346282614</v>
       </c>
       <c r="D2" t="n">
-        <v>28.36465467109885</v>
+        <v>31.16067213279376</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.04666622591412</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C3" t="n">
-        <v>21.06830573313655</v>
+        <v>19.09499284760046</v>
       </c>
       <c r="D3" t="n">
-        <v>46.80482179996669</v>
+        <v>47.05025872602839</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.38428962518378</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="C4" t="n">
-        <v>38.24987230515998</v>
+        <v>40.48334833232148</v>
       </c>
       <c r="D4" t="n">
-        <v>39.66653424238812</v>
+        <v>35.78666731520473</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.18182861393069</v>
+        <v>21.03394456348791</v>
       </c>
       <c r="C5" t="n">
-        <v>43.83503499462009</v>
+        <v>50.70726892434777</v>
       </c>
       <c r="D5" t="n">
-        <v>33.4285093296039</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>8.332092765942681</v>
       </c>
       <c r="C6" t="n">
-        <v>22.42017232188442</v>
+        <v>29.62521872335175</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06962980824325</v>
+        <v>16.09221469645578</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8828230347298</v>
+        <v>101.6350401881418</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88366849837838</v>
+        <v>3.38783467293806</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.784457473422207</v>
+        <v>2.313979338909732</v>
       </c>
       <c r="C2" t="n">
-        <v>8.036586706964391</v>
+        <v>8.650179022118646</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04634743074463</v>
+        <v>29.8107690394544</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.00248757922301</v>
+        <v>9.06153131019806</v>
       </c>
       <c r="C3" t="n">
-        <v>27.47911824186822</v>
+        <v>19.72822011683965</v>
       </c>
       <c r="D3" t="n">
-        <v>54.51645001682538</v>
+        <v>60.26458282519045</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.90082778633785</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="C4" t="n">
-        <v>38.96458463385165</v>
+        <v>44.64399510291945</v>
       </c>
       <c r="D4" t="n">
-        <v>46.29038600294135</v>
+        <v>50.13196476965913</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.81305133003238</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="C5" t="n">
-        <v>43.51596699073988</v>
+        <v>63.96086293167971</v>
       </c>
       <c r="D5" t="n">
-        <v>32.61856747360028</v>
+        <v>35.9810533606456</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.43776166510284</v>
+        <v>18.39500673447249</v>
       </c>
       <c r="C6" t="n">
-        <v>31.71830482880595</v>
+        <v>56.51332484726341</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91327171132357</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>17.36711688812607</v>
+        <v>30.60205768907732</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.82718101298611</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064301441007871</v>
+        <v>17.36779601809193</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22782600944879</v>
+        <v>115.4958435203113</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298226080755904</v>
+        <v>4.341949004522982</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.464988558914493</v>
+        <v>1.990002596508285</v>
       </c>
       <c r="C2" t="n">
-        <v>4.217588137444298</v>
+        <v>9.387471548008001</v>
       </c>
       <c r="D2" t="n">
-        <v>24.60063397301657</v>
+        <v>34.24728691494573</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6679325962531</v>
+        <v>8.408669086873932</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06602344255857</v>
+        <v>27.39566968700725</v>
       </c>
       <c r="D3" t="n">
-        <v>62.86130550292327</v>
+        <v>68.90396262256239</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>20.12680968476386</v>
       </c>
       <c r="C4" t="n">
-        <v>58.10866486666446</v>
+        <v>47.15825097349554</v>
       </c>
       <c r="D4" t="n">
-        <v>65.03882191094269</v>
+        <v>66.5320601691021</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27433388230815</v>
+        <v>31.71045084717198</v>
       </c>
       <c r="C5" t="n">
-        <v>61.28560043760715</v>
+        <v>73.55744674069228</v>
       </c>
       <c r="D5" t="n">
-        <v>42.97600575340413</v>
+        <v>45.3076565509903</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.73589417202438</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>54.13847715069036</v>
+        <v>78.57123226628075</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="C7" t="n">
-        <v>34.2551408965797</v>
+        <v>56.23352675155305</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>21.44627859927157</v>
+        <v>33.12907627980861</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289428980819857</v>
+        <v>18.66595793116707</v>
       </c>
       <c r="C21" t="n">
-        <v>76.5390042986085</v>
+        <v>128.8839952390107</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378250358217374</v>
+        <v>5.333130837476308</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.069745144730529</v>
+        <v>1.849612674800991</v>
       </c>
       <c r="C2" t="n">
-        <v>3.57356164345839</v>
+        <v>5.706899404786709</v>
       </c>
       <c r="D2" t="n">
-        <v>24.35617879465912</v>
+        <v>26.70746454633023</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8811517745239</v>
+        <v>12.46819584393449</v>
       </c>
       <c r="C3" t="n">
-        <v>21.66717183272711</v>
+        <v>41.22849483984481</v>
       </c>
       <c r="D3" t="n">
-        <v>67.95657608796421</v>
+        <v>76.718674348367</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.95334344074844</v>
+        <v>15.22592514516378</v>
       </c>
       <c r="C4" t="n">
-        <v>68.44646819238336</v>
+        <v>66.59587376987814</v>
       </c>
       <c r="D4" t="n">
-        <v>81.32405282898878</v>
+        <v>60.94198874112076</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.63744166415923</v>
+        <v>16.1742934274662</v>
       </c>
       <c r="C5" t="n">
-        <v>88.08731276354507</v>
+        <v>46.92754026299754</v>
       </c>
       <c r="D5" t="n">
-        <v>57.43224069843842</v>
+        <v>36.81553890925539</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>9.177377539299185</v>
       </c>
       <c r="C6" t="n">
-        <v>78.41022564278425</v>
+        <v>37.0315234041897</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>58.38944471007905</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>35.04839304161113</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>25.95937279569415</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.502500803504342</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.27875924029992</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.502500803504342</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
